--- a/Final_Result_Report_Term_V.xlsx
+++ b/Final_Result_Report_Term_V.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Date: 28/03/2026</t>
+          <t>Date: 11/04/2026</t>
         </is>
       </c>
     </row>
